--- a/artfynd/A 9569-2026 artfynd.xlsx
+++ b/artfynd/A 9569-2026 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60791755</v>
+        <v>69506696</v>
       </c>
       <c r="B2" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2058</v>
+        <v>473</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691979.0256163934</v>
+        <v>691994</v>
       </c>
       <c r="R2" t="n">
-        <v>6682835.776265331</v>
+        <v>6682836</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca. 20 ex. i äldre barrskog.</t>
+          <t>2 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,42 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69506696</v>
+        <v>60791755</v>
       </c>
       <c r="B3" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>473</v>
+        <v>2058</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691993.9881527497</v>
+        <v>691979</v>
       </c>
       <c r="R3" t="n">
-        <v>6682835.56826393</v>
+        <v>6682836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,24 +868,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 ex. i äldre barrskog.</t>
+          <t>Ca. 20 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69510694</v>
+        <v>75874046</v>
       </c>
       <c r="B4" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,43 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyren på Söderön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691993.5161967153</v>
+        <v>691989</v>
       </c>
       <c r="R4" t="n">
-        <v>6682825.592216701</v>
+        <v>6682844</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,24 +975,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca. 10 ex. i äldre barrskog.</t>
+          <t>På granstubbe (från nedsågat träd).</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,9 +994,14 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik barrskog.</t>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Granstubbe, från nedsågat träd. # Gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,15 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69510695</v>
+        <v>69507085</v>
       </c>
       <c r="B5" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,26 +1030,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691953.3364746575</v>
+        <v>691994</v>
       </c>
       <c r="R5" t="n">
-        <v>6682821.985991672</v>
+        <v>6682841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,24 +1096,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca. 5 ex. i äldre barrskog.</t>
+          <t>Ca. 10 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,15 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69507085</v>
+        <v>69510694</v>
       </c>
       <c r="B6" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,21 +1146,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1248,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691994.2241290903</v>
+        <v>691994</v>
       </c>
       <c r="R6" t="n">
-        <v>6682840.55627748</v>
+        <v>6682826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1281,19 +1212,9 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2005-09-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1330,15 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69524502</v>
+        <v>69510695</v>
       </c>
       <c r="B7" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,26 +1262,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1379,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691976.4089641555</v>
+        <v>691953</v>
       </c>
       <c r="R7" t="n">
-        <v>6682828.672774047</v>
+        <v>6682822</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1412,24 +1328,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca. 10 ex. i äldre barrskog.</t>
+          <t>Ca. 5 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,42 +1367,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69552910</v>
+        <v>69524502</v>
       </c>
       <c r="B8" t="n">
-        <v>88906</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5745</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1510,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691982.3219805311</v>
+        <v>691976</v>
       </c>
       <c r="R8" t="n">
-        <v>6682839.432587012</v>
+        <v>6682829</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,24 +1444,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2 ex. i äldre barrskog.</t>
+          <t>Ca. 10 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1592,50 +1483,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75874046</v>
+        <v>69552910</v>
       </c>
       <c r="B9" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>5745</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupmyren på Söderön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691989.0713054838</v>
+        <v>691982</v>
       </c>
       <c r="R9" t="n">
-        <v>6682843.768115602</v>
+        <v>6682839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,24 +1560,14 @@
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2005-09-12</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granstubbe (från nedsågat träd).</t>
+          <t>2 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,14 +1579,9 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Granstubbe, från nedsågat träd. # Gran</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 9569-2026 artfynd.xlsx
+++ b/artfynd/A 9569-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506696</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60791755</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75874046</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69507085</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510694</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510695</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69524502</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1596,8 +1636,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69552910</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>